--- a/data/trans_orig/P37A$vacunapreferencia-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P37A$vacunapreferencia-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18737</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>10211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24133</t>
+          <t>24481</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>675275</t>
+          <t>675062</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>688060</t>
+          <t>688024</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>677824</t>
+          <t>678140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>686553</t>
+          <t>686661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1358230</t>
+          <t>1357882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1373463</t>
+          <t>1373622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21909</t>
+          <t>21820</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46088</t>
+          <t>45613</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19099</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40818</t>
+          <t>41285</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45973</t>
+          <t>43900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80322</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>915712</t>
+          <t>916187</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>939891</t>
+          <t>939980</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>927575</t>
+          <t>927108</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>949294</t>
+          <t>950150</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1849871</t>
+          <t>1854820</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1884220</t>
+          <t>1886293</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29529</t>
+          <t>30175</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17374</t>
+          <t>18109</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39078</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34574</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61645</t>
+          <t>62861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>648980</t>
+          <t>648334</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667480</t>
+          <t>666715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>644763</t>
+          <t>645147</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>666467</t>
+          <t>665732</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1300705</t>
+          <t>1299489</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1327776</t>
+          <t>1328021</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40299</t>
+          <t>39879</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17040</t>
+          <t>16871</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40779</t>
+          <t>37644</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41511</t>
+          <t>42577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69965</t>
+          <t>72410</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>901923</t>
+          <t>902343</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>923103</t>
+          <t>923197</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>997833</t>
+          <t>1000968</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1021572</t>
+          <t>1021741</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1910869</t>
+          <t>1908424</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1939323</t>
+          <t>1938257</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74819</t>
+          <t>73364</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>113119</t>
+          <t>111372</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67545</t>
+          <t>69680</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108075</t>
+          <t>105793</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>151285</t>
+          <t>152147</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>205842</t>
+          <t>207189</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3163424</t>
+          <t>3165171</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3201724</t>
+          <t>3203179</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3271122</t>
+          <t>3273404</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3311652</t>
+          <t>3309517</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6449899</t>
+          <t>6448552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6504456</t>
+          <t>6503594</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21156</t>
+          <t>22019</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44971</t>
+          <t>45099</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>21315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32453</t>
+          <t>32432</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60712</t>
+          <t>60072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>658498</t>
+          <t>658370</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>682313</t>
+          <t>681450</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>675282</t>
+          <t>675735</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>689945</t>
+          <t>689919</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1339807</t>
+          <t>1340447</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1368066</t>
+          <t>1368087</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18486</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39092</t>
+          <t>40466</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>13612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32003</t>
+          <t>33098</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37092</t>
+          <t>36258</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66092</t>
+          <t>65380</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>978855</t>
+          <t>977481</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>999461</t>
+          <t>999396</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1000181</t>
+          <t>999086</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1018963</t>
+          <t>1018572</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1984039</t>
+          <t>1984751</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2013039</t>
+          <t>2013873</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>15055</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36616</t>
+          <t>35975</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27121</t>
+          <t>26796</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28887</t>
+          <t>29456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55100</t>
+          <t>55250</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>721007</t>
+          <t>721648</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>741378</t>
+          <t>742568</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>750053</t>
+          <t>750378</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>767327</t>
+          <t>767749</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1479697</t>
+          <t>1479547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1505910</t>
+          <t>1505341</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>12988</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30530</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9656</t>
+          <t>10246</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25995</t>
+          <t>26479</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26207</t>
+          <t>26205</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50852</t>
+          <t>50256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>917209</t>
+          <t>916645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>935196</t>
+          <t>934751</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1025906</t>
+          <t>1025422</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1042245</t>
+          <t>1041655</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1948788</t>
+          <t>1949384</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1973433</t>
+          <t>1973435</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86116</t>
+          <t>83812</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>126484</t>
+          <t>125526</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53628</t>
+          <t>52958</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88684</t>
+          <t>85022</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>147335</t>
+          <t>146471</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>199000</t>
+          <t>200010</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3300295</t>
+          <t>3301253</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3340663</t>
+          <t>3342967</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3469625</t>
+          <t>3473287</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3504681</t>
+          <t>3505351</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6786088</t>
+          <t>6785078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6837753</t>
+          <t>6838617</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8653</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>23647</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>14445</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13943</t>
+          <t>14304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32331</t>
+          <t>33617</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>651048</t>
+          <t>651153</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>666147</t>
+          <t>666860</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>659096</t>
+          <t>658394</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>669940</t>
+          <t>669925</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1315308</t>
+          <t>1314022</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1333696</t>
+          <t>1333335</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19112</t>
+          <t>19665</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14794</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>37270</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24696</t>
+          <t>24978</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50505</t>
+          <t>49933</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1003319</t>
+          <t>1002766</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1017448</t>
+          <t>1017225</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1005845</t>
+          <t>1005643</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1028119</t>
+          <t>1027017</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2014839</t>
+          <t>2015411</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2040648</t>
+          <t>2040366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>14315</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>21393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30829</t>
+          <t>31592</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>745445</t>
+          <t>745237</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>756445</t>
+          <t>756466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>764240</t>
+          <t>763618</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>778605</t>
+          <t>778553</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1513734</t>
+          <t>1512971</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1532099</t>
+          <t>1531729</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>14241</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31289</t>
+          <t>32234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12166</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31767</t>
+          <t>31090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29133</t>
+          <t>29454</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55260</t>
+          <t>56824</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>906278</t>
+          <t>905333</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>923459</t>
+          <t>923326</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1012012</t>
+          <t>1012689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1031613</t>
+          <t>1032250</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1926086</t>
+          <t>1924522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1952213</t>
+          <t>1951892</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42595</t>
+          <t>41274</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73043</t>
+          <t>70793</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49125</t>
+          <t>48741</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82588</t>
+          <t>82379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98108</t>
+          <t>98580</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143223</t>
+          <t>142538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3321307</t>
+          <t>3323557</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3351755</t>
+          <t>3353076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3461954</t>
+          <t>3462163</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3495417</t>
+          <t>3495801</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6795669</t>
+          <t>6796354</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6840784</t>
+          <t>6840312</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>51296</t>
+          <t>56852</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38893</t>
+          <t>42880</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65301</t>
+          <t>71245</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>52931</t>
+          <t>57778</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40107</t>
+          <t>47482</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65271</t>
+          <t>71066</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>104227</t>
+          <t>114630</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85425</t>
+          <t>97327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122721</t>
+          <t>136032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>584145</t>
+          <t>633858</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>570140</t>
+          <t>619465</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>596548</t>
+          <t>647830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>672399</t>
+          <t>676402</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>660059</t>
+          <t>663114</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>685223</t>
+          <t>686698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1256545</t>
+          <t>1310259</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1238051</t>
+          <t>1288857</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1275347</t>
+          <t>1327562</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>64408</t>
+          <t>70607</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31953</t>
+          <t>53376</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89726</t>
+          <t>87566</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68947</t>
+          <t>78460</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57207</t>
+          <t>65756</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83630</t>
+          <t>95861</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>133355</t>
+          <t>149068</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92026</t>
+          <t>129400</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161100</t>
+          <t>172404</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1128456</t>
+          <t>978310</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1103138</t>
+          <t>961351</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1160911</t>
+          <t>995541</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>889704</t>
+          <t>993014</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>875021</t>
+          <t>975613</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>901444</t>
+          <t>1005718</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2018161</t>
+          <t>1971323</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1990416</t>
+          <t>1947987</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2059490</t>
+          <t>1990991</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>65820</t>
+          <t>75348</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50946</t>
+          <t>59073</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82283</t>
+          <t>94986</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>67171</t>
+          <t>72940</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32436</t>
+          <t>58532</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93852</t>
+          <t>88970</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>132992</t>
+          <t>148288</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87714</t>
+          <t>125713</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163976</t>
+          <t>171763</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>638860</t>
+          <t>727725</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>622397</t>
+          <t>708087</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>653734</t>
+          <t>744000</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>866195</t>
+          <t>739319</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>839514</t>
+          <t>723289</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>900930</t>
+          <t>753727</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1505054</t>
+          <t>1467044</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1474070</t>
+          <t>1443569</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1550332</t>
+          <t>1489619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70328</t>
+          <t>74470</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58075</t>
+          <t>58429</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91743</t>
+          <t>89816</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>76044</t>
+          <t>84367</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60223</t>
+          <t>68857</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92170</t>
+          <t>99113</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>146372</t>
+          <t>158838</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122341</t>
+          <t>138193</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167699</t>
+          <t>182034</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>856503</t>
+          <t>915592</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>835088</t>
+          <t>900246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>868756</t>
+          <t>931633</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1018888</t>
+          <t>1034674</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1002762</t>
+          <t>1019928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1034709</t>
+          <t>1050184</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1875391</t>
+          <t>1950266</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1854064</t>
+          <t>1927070</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1899422</t>
+          <t>1970911</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>251852</t>
+          <t>277278</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>199770</t>
+          <t>245821</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>288312</t>
+          <t>310395</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>265094</t>
+          <t>293546</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>211722</t>
+          <t>266758</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>296987</t>
+          <t>325441</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>7,14%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>516946</t>
+          <t>570824</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>448678</t>
+          <t>530256</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>571131</t>
+          <t>616274</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3207965</t>
+          <t>3255484</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3171505</t>
+          <t>3222367</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3260047</t>
+          <t>3286941</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,34 +8089,34 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3447186</t>
+          <t>3443408</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3415293</t>
+          <t>3411513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3500558</t>
+          <t>3470196</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>91,29%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>92,86%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>92,0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>8018</t>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6655151</t>
+          <t>6698892</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6600966</t>
+          <t>6653442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6723419</t>
+          <t>6739460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
